--- a/final_outputs/excel_tables/tables_stationarity.xlsx
+++ b/final_outputs/excel_tables/tables_stationarity.xlsx
@@ -467,13 +467,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-13.2684</v>
+        <v>-13.5226</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-58.1759</v>
+        <v>-212.0164</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -491,13 +491,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-14.498</v>
+        <v>-14.7088</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-66.3631</v>
+        <v>-67.1942</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -515,13 +515,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-59.8097</v>
+        <v>-60.8838</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-59.8844</v>
+        <v>-60.9814</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -539,13 +539,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-10.5423</v>
+        <v>-11.1466</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-57.1782</v>
+        <v>-57.9748</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -563,13 +563,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-58.1564</v>
+        <v>-25.3159</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-58.1817</v>
+        <v>-59.5131</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -587,13 +587,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-11.1314</v>
+        <v>-11.2273</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-61.6132</v>
+        <v>-62.3257</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>

--- a/final_outputs/excel_tables/tables_stationarity.xlsx
+++ b/final_outputs/excel_tables/tables_stationarity.xlsx
@@ -467,13 +467,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-13.5226</v>
+        <v>-11.8082</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-212.0164</v>
+        <v>-60.6926</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
